--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -37950,7 +37950,7 @@
         <v>46276.5625</v>
       </c>
       <c r="B1446" t="n">
-        <v>4940434</v>
+        <v>5131900</v>
       </c>
       <c r="C1446" t="n">
         <v>10.8149995803833</v>
@@ -37968,6 +37968,32 @@
         <v>10.539999961853</v>
       </c>
       <c r="H1446" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="1" t="n">
+        <v>46279.5625</v>
+      </c>
+      <c r="B1447" t="n">
+        <v>5657700</v>
+      </c>
+      <c r="C1447" t="n">
+        <v>11.375</v>
+      </c>
+      <c r="D1447" t="n">
+        <v>10.5299997329712</v>
+      </c>
+      <c r="E1447" t="n">
+        <v>10.5200004577637</v>
+      </c>
+      <c r="F1447" t="n">
+        <v>11.1700000762939</v>
+      </c>
+      <c r="G1447" t="n">
+        <v>11.1700000762939</v>
+      </c>
+      <c r="H1447" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -37976,13 +37976,13 @@
         <v>46279.5625</v>
       </c>
       <c r="B1447" t="n">
-        <v>5657700</v>
+        <v>5662500</v>
       </c>
       <c r="C1447" t="n">
         <v>11.375</v>
       </c>
       <c r="D1447" t="n">
-        <v>10.5299997329712</v>
+        <v>10.5200004577637</v>
       </c>
       <c r="E1447" t="n">
         <v>10.5200004577637</v>
@@ -37994,6 +37994,32 @@
         <v>11.1700000762939</v>
       </c>
       <c r="H1447" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="1" t="n">
+        <v>46280.5625</v>
+      </c>
+      <c r="B1448" t="n">
+        <v>4394891</v>
+      </c>
+      <c r="C1448" t="n">
+        <v>11.1199998855591</v>
+      </c>
+      <c r="D1448" t="n">
+        <v>10.7399997711182</v>
+      </c>
+      <c r="E1448" t="n">
+        <v>10.9700002670288</v>
+      </c>
+      <c r="F1448" t="n">
+        <v>10.789999961853</v>
+      </c>
+      <c r="G1448" t="n">
+        <v>10.789999961853</v>
+      </c>
+      <c r="H1448" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38002,7 +38002,7 @@
         <v>46280.5625</v>
       </c>
       <c r="B1448" t="n">
-        <v>4394891</v>
+        <v>4407600</v>
       </c>
       <c r="C1448" t="n">
         <v>11.1199998855591</v>
@@ -38020,6 +38020,32 @@
         <v>10.789999961853</v>
       </c>
       <c r="H1448" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="1" t="n">
+        <v>46281.5625</v>
+      </c>
+      <c r="B1449" t="n">
+        <v>4466471</v>
+      </c>
+      <c r="C1449" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="D1449" t="n">
+        <v>10.3450002670288</v>
+      </c>
+      <c r="E1449" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="F1449" t="n">
+        <v>10.5600004196167</v>
+      </c>
+      <c r="G1449" t="n">
+        <v>10.5600004196167</v>
+      </c>
+      <c r="H1449" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38028,7 +38028,7 @@
         <v>46281.5625</v>
       </c>
       <c r="B1449" t="n">
-        <v>4466471</v>
+        <v>4479200</v>
       </c>
       <c r="C1449" t="n">
         <v>10.75</v>
@@ -38046,6 +38046,32 @@
         <v>10.5600004196167</v>
       </c>
       <c r="H1449" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="1" t="n">
+        <v>46282.5625</v>
+      </c>
+      <c r="B1450" t="n">
+        <v>2931915</v>
+      </c>
+      <c r="C1450" t="n">
+        <v>10.8999996185303</v>
+      </c>
+      <c r="D1450" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1450" t="n">
+        <v>10.6300001144409</v>
+      </c>
+      <c r="F1450" t="n">
+        <v>10.7799997329712</v>
+      </c>
+      <c r="G1450" t="n">
+        <v>10.7799997329712</v>
+      </c>
+      <c r="H1450" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38054,7 +38054,7 @@
         <v>46282.5625</v>
       </c>
       <c r="B1450" t="n">
-        <v>2931915</v>
+        <v>2933700</v>
       </c>
       <c r="C1450" t="n">
         <v>10.8999996185303</v>
@@ -38072,6 +38072,32 @@
         <v>10.7799997329712</v>
       </c>
       <c r="H1450" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="1" t="n">
+        <v>46283.5625</v>
+      </c>
+      <c r="B1451" t="n">
+        <v>9731887</v>
+      </c>
+      <c r="C1451" t="n">
+        <v>11.0799999237061</v>
+      </c>
+      <c r="D1451" t="n">
+        <v>10.4350004196167</v>
+      </c>
+      <c r="E1451" t="n">
+        <v>10.8500003814697</v>
+      </c>
+      <c r="F1451" t="n">
+        <v>10.4799995422363</v>
+      </c>
+      <c r="G1451" t="n">
+        <v>10.4799995422363</v>
+      </c>
+      <c r="H1451" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38080,7 +38080,7 @@
         <v>46283.5625</v>
       </c>
       <c r="B1451" t="n">
-        <v>9731887</v>
+        <v>9743600</v>
       </c>
       <c r="C1451" t="n">
         <v>11.0799999237061</v>
@@ -38098,6 +38098,32 @@
         <v>10.4799995422363</v>
       </c>
       <c r="H1451" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="1" t="n">
+        <v>46286.5625</v>
+      </c>
+      <c r="B1452" t="n">
+        <v>4230689</v>
+      </c>
+      <c r="C1452" t="n">
+        <v>10.9700002670288</v>
+      </c>
+      <c r="D1452" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1452" t="n">
+        <v>10.6800003051758</v>
+      </c>
+      <c r="F1452" t="n">
+        <v>10.8400001525879</v>
+      </c>
+      <c r="G1452" t="n">
+        <v>10.8400001525879</v>
+      </c>
+      <c r="H1452" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38106,13 +38106,13 @@
         <v>46286.5625</v>
       </c>
       <c r="B1452" t="n">
-        <v>4230689</v>
+        <v>4232300</v>
       </c>
       <c r="C1452" t="n">
         <v>10.9700002670288</v>
       </c>
       <c r="D1452" t="n">
-        <v>10.5</v>
+        <v>10.4899997711182</v>
       </c>
       <c r="E1452" t="n">
         <v>10.6800003051758</v>
@@ -38124,6 +38124,32 @@
         <v>10.8400001525879</v>
       </c>
       <c r="H1452" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="1" t="n">
+        <v>46287.5625</v>
+      </c>
+      <c r="B1453" t="n">
+        <v>4025401</v>
+      </c>
+      <c r="C1453" t="n">
+        <v>11.1199998855591</v>
+      </c>
+      <c r="D1453" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="E1453" t="n">
+        <v>11.039999961853</v>
+      </c>
+      <c r="F1453" t="n">
+        <v>10.8500003814697</v>
+      </c>
+      <c r="G1453" t="n">
+        <v>10.8500003814697</v>
+      </c>
+      <c r="H1453" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -33773,10 +33773,10 @@
         <v>46288.5625</v>
       </c>
       <c r="B1453" t="n">
-        <v>3092983</v>
+        <v>3093000</v>
       </c>
       <c r="C1453" t="n">
-        <v>11.0166997909546</v>
+        <v>11.0170001983643</v>
       </c>
       <c r="D1453" t="n">
         <v>10.6400003433228</v>
@@ -33788,6 +33788,29 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1453" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="1" t="n">
+        <v>46289.5625</v>
+      </c>
+      <c r="B1454" t="n">
+        <v>2809306</v>
+      </c>
+      <c r="C1454" t="n">
+        <v>10.9635000228882</v>
+      </c>
+      <c r="D1454" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="E1454" t="n">
+        <v>10.8299999237061</v>
+      </c>
+      <c r="F1454" t="n">
+        <v>10.7600002288818</v>
+      </c>
+      <c r="G1454" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38210,7 +38210,7 @@
         <v>46290.5625</v>
       </c>
       <c r="B1456" t="n">
-        <v>4276912</v>
+        <v>4278400</v>
       </c>
       <c r="C1456" t="n">
         <v>10.8149995803833</v>
@@ -38228,6 +38228,32 @@
         <v>10.6499996185303</v>
       </c>
       <c r="H1456" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="1" t="n">
+        <v>46293.5625</v>
+      </c>
+      <c r="B1457" t="n">
+        <v>3413739</v>
+      </c>
+      <c r="C1457" t="n">
+        <v>10.5389995574951</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>10.4499998092651</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>10.4099998474121</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>10.4099998474121</v>
+      </c>
+      <c r="H1457" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38236,7 +38236,7 @@
         <v>46293.5625</v>
       </c>
       <c r="B1457" t="n">
-        <v>3413739</v>
+        <v>3415800</v>
       </c>
       <c r="C1457" t="n">
         <v>10.5389995574951</v>
@@ -38254,6 +38254,32 @@
         <v>10.4099998474121</v>
       </c>
       <c r="H1457" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="1" t="n">
+        <v>46294.5625</v>
+      </c>
+      <c r="B1458" t="n">
+        <v>3581572</v>
+      </c>
+      <c r="C1458" t="n">
+        <v>10.7399997711182</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>10.2349996566772</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>10.3800001144409</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>10.3400001525879</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>10.3400001525879</v>
+      </c>
+      <c r="H1458" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38262,7 +38262,7 @@
         <v>46294.5625</v>
       </c>
       <c r="B1458" t="n">
-        <v>3581572</v>
+        <v>3582800</v>
       </c>
       <c r="C1458" t="n">
         <v>10.7399997711182</v>
@@ -38280,6 +38280,32 @@
         <v>10.3400001525879</v>
       </c>
       <c r="H1458" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="1" t="n">
+        <v>46295.5625</v>
+      </c>
+      <c r="B1459" t="n">
+        <v>5310546</v>
+      </c>
+      <c r="C1459" t="n">
+        <v>11.0550003051758</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>10.4200000762939</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>10.4499998092651</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>10.9899997711182</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>10.9899997711182</v>
+      </c>
+      <c r="H1459" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38288,10 +38288,10 @@
         <v>46295.5625</v>
       </c>
       <c r="B1459" t="n">
-        <v>5310546</v>
+        <v>5330600</v>
       </c>
       <c r="C1459" t="n">
-        <v>11.0550003051758</v>
+        <v>11.0600004196167</v>
       </c>
       <c r="D1459" t="n">
         <v>10.4200000762939</v>
@@ -38306,6 +38306,32 @@
         <v>10.9899997711182</v>
       </c>
       <c r="H1459" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="1" t="n">
+        <v>46296.5625</v>
+      </c>
+      <c r="B1460" t="n">
+        <v>5839474</v>
+      </c>
+      <c r="C1460" t="n">
+        <v>11.2749996185303</v>
+      </c>
+      <c r="D1460" t="n">
+        <v>10.6549997329712</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>10.9799995422363</v>
+      </c>
+      <c r="F1460" t="n">
+        <v>11.1099996566772</v>
+      </c>
+      <c r="G1460" t="n">
+        <v>11.1099996566772</v>
+      </c>
+      <c r="H1460" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38314,13 +38314,13 @@
         <v>46296.5625</v>
       </c>
       <c r="B1460" t="n">
-        <v>5839474</v>
+        <v>5840700</v>
       </c>
       <c r="C1460" t="n">
         <v>11.2749996185303</v>
       </c>
       <c r="D1460" t="n">
-        <v>10.6549997329712</v>
+        <v>10.6450004577637</v>
       </c>
       <c r="E1460" t="n">
         <v>10.9799995422363</v>
@@ -38332,6 +38332,32 @@
         <v>11.1099996566772</v>
       </c>
       <c r="H1460" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="1" t="n">
+        <v>46297.5625</v>
+      </c>
+      <c r="B1461" t="n">
+        <v>5528114</v>
+      </c>
+      <c r="C1461" t="n">
+        <v>11.3800001144409</v>
+      </c>
+      <c r="D1461" t="n">
+        <v>10.9700002670288</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>11.1829996109009</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>11.0100002288818</v>
+      </c>
+      <c r="G1461" t="n">
+        <v>11.0100002288818</v>
+      </c>
+      <c r="H1461" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38340,7 +38340,7 @@
         <v>46297.5625</v>
       </c>
       <c r="B1461" t="n">
-        <v>5528114</v>
+        <v>5535700</v>
       </c>
       <c r="C1461" t="n">
         <v>11.3800001144409</v>
@@ -38358,6 +38358,32 @@
         <v>11.0100002288818</v>
       </c>
       <c r="H1461" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="1" t="n">
+        <v>46300.5625</v>
+      </c>
+      <c r="B1462" t="n">
+        <v>3690464</v>
+      </c>
+      <c r="C1462" t="n">
+        <v>11.2864999771118</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>10.875</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>11.0500001907349</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>11.0900001525879</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>11.0900001525879</v>
+      </c>
+      <c r="H1462" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38366,10 +38366,10 @@
         <v>46300.5625</v>
       </c>
       <c r="B1462" t="n">
-        <v>3690464</v>
+        <v>3691200</v>
       </c>
       <c r="C1462" t="n">
-        <v>11.2864999771118</v>
+        <v>11.2869997024536</v>
       </c>
       <c r="D1462" t="n">
         <v>10.875</v>
@@ -38384,6 +38384,32 @@
         <v>11.0900001525879</v>
       </c>
       <c r="H1462" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="1" t="n">
+        <v>46301.5625</v>
+      </c>
+      <c r="B1463" t="n">
+        <v>3678094</v>
+      </c>
+      <c r="C1463" t="n">
+        <v>11.4700002670288</v>
+      </c>
+      <c r="D1463" t="n">
+        <v>11.1899995803833</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>11.2399997711182</v>
+      </c>
+      <c r="F1463" t="n">
+        <v>11.2399997711182</v>
+      </c>
+      <c r="G1463" t="n">
+        <v>11.2399997711182</v>
+      </c>
+      <c r="H1463" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38392,7 +38392,7 @@
         <v>46301.5625</v>
       </c>
       <c r="B1463" t="n">
-        <v>3678094</v>
+        <v>3686100</v>
       </c>
       <c r="C1463" t="n">
         <v>11.4700002670288</v>
@@ -38410,6 +38410,32 @@
         <v>11.2399997711182</v>
       </c>
       <c r="H1463" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="1" t="n">
+        <v>46302.5625</v>
+      </c>
+      <c r="B1464" t="n">
+        <v>2977243</v>
+      </c>
+      <c r="C1464" t="n">
+        <v>11.4399995803833</v>
+      </c>
+      <c r="D1464" t="n">
+        <v>11.1800003051758</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>11.1899995803833</v>
+      </c>
+      <c r="F1464" t="n">
+        <v>11.2299995422363</v>
+      </c>
+      <c r="G1464" t="n">
+        <v>11.2299995422363</v>
+      </c>
+      <c r="H1464" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38418,13 +38418,13 @@
         <v>46302.5625</v>
       </c>
       <c r="B1464" t="n">
-        <v>2977243</v>
+        <v>2978200</v>
       </c>
       <c r="C1464" t="n">
         <v>11.4399995803833</v>
       </c>
       <c r="D1464" t="n">
-        <v>11.1800003051758</v>
+        <v>11.1750001907349</v>
       </c>
       <c r="E1464" t="n">
         <v>11.1899995803833</v>
@@ -38436,6 +38436,32 @@
         <v>11.2299995422363</v>
       </c>
       <c r="H1464" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="1" t="n">
+        <v>46303.5625</v>
+      </c>
+      <c r="B1465" t="n">
+        <v>4448058</v>
+      </c>
+      <c r="C1465" t="n">
+        <v>11.4200000762939</v>
+      </c>
+      <c r="D1465" t="n">
+        <v>10.9714002609253</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>11.1800003051758</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>11.3400001525879</v>
+      </c>
+      <c r="G1465" t="n">
+        <v>11.3400001525879</v>
+      </c>
+      <c r="H1465" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38444,13 +38444,13 @@
         <v>46303.5625</v>
       </c>
       <c r="B1465" t="n">
-        <v>4448058</v>
+        <v>4448600</v>
       </c>
       <c r="C1465" t="n">
         <v>11.4200000762939</v>
       </c>
       <c r="D1465" t="n">
-        <v>10.9714002609253</v>
+        <v>10.9700002670288</v>
       </c>
       <c r="E1465" t="n">
         <v>11.1800003051758</v>
@@ -38462,6 +38462,32 @@
         <v>11.3400001525879</v>
       </c>
       <c r="H1465" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="1" t="n">
+        <v>46304.5625</v>
+      </c>
+      <c r="B1466" t="n">
+        <v>4468113</v>
+      </c>
+      <c r="C1466" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>11.4300003051758</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>11.3699998855591</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>11.5299997329712</v>
+      </c>
+      <c r="G1466" t="n">
+        <v>11.5299997329712</v>
+      </c>
+      <c r="H1466" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38470,13 +38470,13 @@
         <v>46304.5625</v>
       </c>
       <c r="B1466" t="n">
-        <v>4468113</v>
+        <v>4473000</v>
       </c>
       <c r="C1466" t="n">
         <v>11.75</v>
       </c>
       <c r="D1466" t="n">
-        <v>11.4300003051758</v>
+        <v>11.3699998855591</v>
       </c>
       <c r="E1466" t="n">
         <v>11.3699998855591</v>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38522,13 +38522,13 @@
         <v>46308.5625</v>
       </c>
       <c r="B1468" t="n">
-        <v>7121540</v>
+        <v>7122500</v>
       </c>
       <c r="C1468" t="n">
-        <v>12.0150003433228</v>
+        <v>12.0200004577637</v>
       </c>
       <c r="D1468" t="n">
-        <v>11.5200004577637</v>
+        <v>11.5100002288818</v>
       </c>
       <c r="E1468" t="n">
         <v>11.6300001144409</v>
@@ -38540,6 +38540,32 @@
         <v>12.0100002288818</v>
       </c>
       <c r="H1468" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="1" t="n">
+        <v>46309.5625</v>
+      </c>
+      <c r="B1469" t="n">
+        <v>5320093</v>
+      </c>
+      <c r="C1469" t="n">
+        <v>12.1254997253418</v>
+      </c>
+      <c r="D1469" t="n">
+        <v>11.5600004196167</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="F1469" t="n">
+        <v>11.6700000762939</v>
+      </c>
+      <c r="G1469" t="n">
+        <v>11.6700000762939</v>
+      </c>
+      <c r="H1469" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38548,10 +38548,10 @@
         <v>46309.5625</v>
       </c>
       <c r="B1469" t="n">
-        <v>5320093</v>
+        <v>5324100</v>
       </c>
       <c r="C1469" t="n">
-        <v>12.1254997253418</v>
+        <v>12.1300001144409</v>
       </c>
       <c r="D1469" t="n">
         <v>11.5600004196167</v>
@@ -38566,6 +38566,32 @@
         <v>11.6700000762939</v>
       </c>
       <c r="H1469" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="1" t="n">
+        <v>46310.5625</v>
+      </c>
+      <c r="B1470" t="n">
+        <v>5938503</v>
+      </c>
+      <c r="C1470" t="n">
+        <v>12.2399997711182</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>11.3400001525879</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>11.4350004196167</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>12.1599998474121</v>
+      </c>
+      <c r="G1470" t="n">
+        <v>12.1599998474121</v>
+      </c>
+      <c r="H1470" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -38574,10 +38574,10 @@
         <v>46310.5625</v>
       </c>
       <c r="B1470" t="n">
-        <v>5938503</v>
+        <v>5939600</v>
       </c>
       <c r="C1470" t="n">
-        <v>12.2399997711182</v>
+        <v>12.2449998855591</v>
       </c>
       <c r="D1470" t="n">
         <v>11.3400001525879</v>
@@ -38592,6 +38592,32 @@
         <v>12.1599998474121</v>
       </c>
       <c r="H1470" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="1" t="n">
+        <v>46311.5625</v>
+      </c>
+      <c r="B1471" t="n">
+        <v>9693343</v>
+      </c>
+      <c r="C1471" t="n">
+        <v>12.3900003433228</v>
+      </c>
+      <c r="D1471" t="n">
+        <v>10.961199760437</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>12.1899995803833</v>
+      </c>
+      <c r="F1471" t="n">
+        <v>11.3199996948242</v>
+      </c>
+      <c r="G1471" t="n">
+        <v>11.3199996948242</v>
+      </c>
+      <c r="H1471" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -43031,7 +43031,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="H1471" t="n">
-        <v>9715600</v>
+        <v>9728900</v>
       </c>
       <c r="I1471" t="s">
         <v>9</v>
@@ -43051,7 +43051,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="E1472" t="n">
-        <v>11.2399997711182</v>
+        <v>11.2299995422363</v>
       </c>
       <c r="F1472" t="n">
         <v>11.2799997329712</v>
@@ -43060,9 +43060,38 @@
         <v>11.2799997329712</v>
       </c>
       <c r="H1472" t="n">
-        <v>3551201</v>
+        <v>3551500</v>
       </c>
       <c r="I1472" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1473" s="1" t="n">
+        <v>46315.5625</v>
+      </c>
+      <c r="C1473" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="D1473" t="n">
+        <v>11.8175001144409</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>11.1599998474121</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>11.6899995803833</v>
+      </c>
+      <c r="G1473" t="n">
+        <v>11.6899995803833</v>
+      </c>
+      <c r="H1473" t="n">
+        <v>3716261</v>
+      </c>
+      <c r="I1473" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -43077,7 +43077,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="D1473" t="n">
-        <v>11.8175001144409</v>
+        <v>11.8179998397827</v>
       </c>
       <c r="E1473" t="n">
         <v>11.1599998474121</v>
@@ -43089,9 +43089,38 @@
         <v>11.6899995803833</v>
       </c>
       <c r="H1473" t="n">
-        <v>3716261</v>
+        <v>3717000</v>
       </c>
       <c r="I1473" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1474" s="1" t="n">
+        <v>46316.5625</v>
+      </c>
+      <c r="C1474" t="n">
+        <v>11.7700004577637</v>
+      </c>
+      <c r="D1474" t="n">
+        <v>11.9700002670288</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>11.539999961853</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>11.789999961853</v>
+      </c>
+      <c r="G1474" t="n">
+        <v>11.789999961853</v>
+      </c>
+      <c r="H1474" t="n">
+        <v>3325903</v>
+      </c>
+      <c r="I1474" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -43109,7 +43109,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="E1474" t="n">
-        <v>11.539999961853</v>
+        <v>11.5299997329712</v>
       </c>
       <c r="F1474" t="n">
         <v>11.789999961853</v>
@@ -43118,9 +43118,38 @@
         <v>11.789999961853</v>
       </c>
       <c r="H1474" t="n">
-        <v>3325903</v>
+        <v>3330800</v>
       </c>
       <c r="I1474" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1475" s="1" t="n">
+        <v>46317.5625</v>
+      </c>
+      <c r="C1475" t="n">
+        <v>11.710000038147</v>
+      </c>
+      <c r="D1475" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>11.6279001235962</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>12.0299997329712</v>
+      </c>
+      <c r="G1475" t="n">
+        <v>12.0299997329712</v>
+      </c>
+      <c r="H1475" t="n">
+        <v>4702539</v>
+      </c>
+      <c r="I1475" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -43138,7 +43138,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="E1475" t="n">
-        <v>11.6279001235962</v>
+        <v>11.6280002593994</v>
       </c>
       <c r="F1475" t="n">
         <v>12.0299997329712</v>
@@ -43147,9 +43147,38 @@
         <v>12.0299997329712</v>
       </c>
       <c r="H1475" t="n">
-        <v>4702539</v>
+        <v>4703800</v>
       </c>
       <c r="I1475" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1476" s="1" t="n">
+        <v>46318.5625</v>
+      </c>
+      <c r="C1476" t="n">
+        <v>11.9099998474121</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>12.4949998855591</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>11.8400001525879</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>12.460000038147</v>
+      </c>
+      <c r="G1476" t="n">
+        <v>12.460000038147</v>
+      </c>
+      <c r="H1476" t="n">
+        <v>5843049</v>
+      </c>
+      <c r="I1476" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -43164,10 +43164,10 @@
         <v>11.9099998474121</v>
       </c>
       <c r="D1476" t="n">
-        <v>12.4949998855591</v>
+        <v>12.5</v>
       </c>
       <c r="E1476" t="n">
-        <v>11.8400001525879</v>
+        <v>11.8299999237061</v>
       </c>
       <c r="F1476" t="n">
         <v>12.460000038147</v>
@@ -43176,9 +43176,38 @@
         <v>12.460000038147</v>
       </c>
       <c r="H1476" t="n">
-        <v>5843049</v>
+        <v>5846700</v>
       </c>
       <c r="I1476" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1477" s="1" t="n">
+        <v>46321.5625</v>
+      </c>
+      <c r="C1477" t="n">
+        <v>12.3699998855591</v>
+      </c>
+      <c r="D1477" t="n">
+        <v>13.0349998474121</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>12.3500003814697</v>
+      </c>
+      <c r="F1477" t="n">
+        <v>12.789999961853</v>
+      </c>
+      <c r="G1477" t="n">
+        <v>12.789999961853</v>
+      </c>
+      <c r="H1477" t="n">
+        <v>5150370</v>
+      </c>
+      <c r="I1477" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -43193,7 +43193,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="D1477" t="n">
-        <v>13.0349998474121</v>
+        <v>13.039999961853</v>
       </c>
       <c r="E1477" t="n">
         <v>12.3500003814697</v>
@@ -43205,9 +43205,38 @@
         <v>12.789999961853</v>
       </c>
       <c r="H1477" t="n">
-        <v>5150370</v>
+        <v>5154500</v>
       </c>
       <c r="I1477" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1478" s="1" t="n">
+        <v>46322.5625</v>
+      </c>
+      <c r="C1478" t="n">
+        <v>12.7299995422363</v>
+      </c>
+      <c r="D1478" t="n">
+        <v>12.8549995422363</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>12.2799997329712</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>12.289999961853</v>
+      </c>
+      <c r="G1478" t="n">
+        <v>12.289999961853</v>
+      </c>
+      <c r="H1478" t="n">
+        <v>5973179</v>
+      </c>
+      <c r="I1478" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -43225,7 +43225,7 @@
         <v>12.8549995422363</v>
       </c>
       <c r="E1478" t="n">
-        <v>12.2799997329712</v>
+        <v>11.7399997711182</v>
       </c>
       <c r="F1478" t="n">
         <v>12.289999961853</v>
@@ -43234,9 +43234,38 @@
         <v>12.289999961853</v>
       </c>
       <c r="H1478" t="n">
-        <v>5973179</v>
+        <v>5976100</v>
       </c>
       <c r="I1478" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1479" s="1" t="n">
+        <v>46323.5625</v>
+      </c>
+      <c r="C1479" t="n">
+        <v>12.3400001525879</v>
+      </c>
+      <c r="D1479" t="n">
+        <v>12.5586004257202</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>12.0249996185303</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>12.3299999237061</v>
+      </c>
+      <c r="G1479" t="n">
+        <v>12.3299999237061</v>
+      </c>
+      <c r="H1479" t="n">
+        <v>4235630</v>
+      </c>
+      <c r="I1479" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -43251,7 +43251,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="D1479" t="n">
-        <v>12.5586004257202</v>
+        <v>12.5590000152588</v>
       </c>
       <c r="E1479" t="n">
         <v>12.0249996185303</v>
@@ -43263,9 +43263,38 @@
         <v>12.3299999237061</v>
       </c>
       <c r="H1479" t="n">
-        <v>4235630</v>
+        <v>4250200</v>
       </c>
       <c r="I1479" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1480" s="1" t="n">
+        <v>46324.5625</v>
+      </c>
+      <c r="C1480" t="n">
+        <v>12.2299995422363</v>
+      </c>
+      <c r="D1480" t="n">
+        <v>12.3199996948242</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>11.9820003509521</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>12.1700000762939</v>
+      </c>
+      <c r="G1480" t="n">
+        <v>12.1700000762939</v>
+      </c>
+      <c r="H1480" t="n">
+        <v>3660734</v>
+      </c>
+      <c r="I1480" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AI.xlsx
+++ b/data/AI.xlsx
@@ -43283,7 +43283,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="E1480" t="n">
-        <v>11.9820003509521</v>
+        <v>11.9799995422363</v>
       </c>
       <c r="F1480" t="n">
         <v>12.1700000762939</v>
@@ -43292,9 +43292,38 @@
         <v>12.1700000762939</v>
       </c>
       <c r="H1480" t="n">
-        <v>3660734</v>
+        <v>3675400</v>
       </c>
       <c r="I1480" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1481" s="1" t="n">
+        <v>46325.5625</v>
+      </c>
+      <c r="C1481" t="n">
+        <v>11.9200000762939</v>
+      </c>
+      <c r="D1481" t="n">
+        <v>12.0799999237061</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>11.3900003433228</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>11.8500003814697</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>11.8500003814697</v>
+      </c>
+      <c r="H1481" t="n">
+        <v>4478021</v>
+      </c>
+      <c r="I1481" t="s">
         <v>9</v>
       </c>
     </row>
